--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A740B1-52DF-44FD-A917-9A5FE515E9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A345AD6B495DA71D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A86091-D6AB-4865-8AC7-89411BE65C68}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 09-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 14-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A345AD6B495DA71D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A86091-D6AB-4865-8AC7-89411BE65C68}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A34654EF58FA870D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7B15DC-822A-40B8-ADB4-A4849F1719A1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A34654EF58FA870D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7B15DC-822A-40B8-ADB4-A4849F1719A1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CDC0CF-95F9-4C99-9E01-BEFBA2650975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CDC0CF-95F9-4C99-9E01-BEFBA2650975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D92FF9A-83B1-420A-8701-DA42676CA332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 14-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 17-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D92FF9A-83B1-420A-8701-DA42676CA332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19357CC9-A759-4630-AC60-3388493DEB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19357CC9-A759-4630-AC60-3388493DEB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A34FC4E75995A70D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56889E91-AA3F-40B5-A3E9-742D6BF6C96B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 17-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 18-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A34FC4E75995A70D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56889E91-AA3F-40B5-A3E9-742D6BF6C96B}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A3457F6F5B59670D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1604C6A-AE5B-4CCA-885F-E3EDCA85899E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 18-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 21-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A3457F6F5B59670D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1604C6A-AE5B-4CCA-885F-E3EDCA85899E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ED2A77-4F7D-4FE2-96C1-9C1E68E23C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ED2A77-4F7D-4FE2-96C1-9C1E68E23C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5736554D-1C3A-4E3F-8260-63AC4644AF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 21-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 22-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5736554D-1C3A-4E3F-8260-63AC4644AF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADC93F3-3DBC-4A4B-943B-056078432C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADC93F3-3DBC-4A4B-943B-056078432C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5419D9C-894A-43DB-8D46-B8BBD9BCC752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 22-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 23-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5419D9C-894A-43DB-8D46-B8BBD9BCC752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A34619EB3AD1070D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E450F1D-A961-4CD5-834F-B4398D7AAA17}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99F0D75F76F4A34619EB3AD1070D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E450F1D-A961-4CD5-834F-B4398D7AAA17}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DE6D31FF914A34955EF08ECC71D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA56A004-AF24-4E93-8B74-D05B89E0C8FF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 23-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 24-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -178,7 +178,7 @@
     <t>XRPT07 (XR0731G)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DE6D31FF914A34955EF08ECC71D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA56A004-AF24-4E93-8B74-D05B89E0C8FF}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DE6D31FF914A34321671944870D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92B6BD7A-0C49-4ED1-A4EF-6DA39E078341}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DE6D31FF914A34321671944870D86EE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92B6BD7A-0C49-4ED1-A4EF-6DA39E078341}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77F0E08-C80D-4E76-BD47-E8598254E34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 24-09-2026'!$A$1:$Y$32</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 28-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -948,7 +948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99BDDFDBD0FCB2D9EFEB2A09E70D86F41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CB3F4BD-DC36-4B55-A297-167640E6D751}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D36C26-555A-4714-B22E-6AA61DEFEBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 02-10-2026'!$A$1:$Z$33</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 07-10-2026'!$A$1:$Z$33</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -587,9 +587,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -731,7 +731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -793,7 +793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -822,7 +822,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -836,7 +836,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -886,7 +886,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -909,7 +909,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -926,7 +926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -940,7 +940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -957,7 +957,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -971,7 +971,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -985,7 +985,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -999,7 +999,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D36C26-555A-4714-B22E-6AA61DEFEBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99BDDFDBD0FCB2DACD6B4AF1E71D86F4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84858227-BD8A-4E6C-8F66-CF9D5FCADFEF}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 07-10-2026'!$A$1:$Z$33</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 08-10-2026'!$A$1:$Z$33</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB99BDDFDBD0FCB2DACD6B4AF1E71D86F4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84858227-BD8A-4E6C-8F66-CF9D5FCADFEF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797F3F23-CC1C-4C65-A94F-F8AFC2A90027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 08-10-2026'!$A$1:$Z$33</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 09-10-2026'!$A$1:$Z$33</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="74">
   <si>
     <t>Standard</t>
   </si>
@@ -835,6 +835,9 @@
       <c r="D5" t="s">
         <v>29</v>
       </c>
+      <c r="X5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1112,6 +1115,9 @@
         <v>29</v>
       </c>
       <c r="U17" t="s">
+        <v>29</v>
+      </c>
+      <c r="X17" t="s">
         <v>29</v>
       </c>
     </row>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797F3F23-CC1C-4C65-A94F-F8AFC2A90027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C62665-FC75-4664-B828-8EB8D78B6732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C62665-FC75-4664-B828-8EB8D78B6732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9A5B5BE9659CA2D4AA6B3AFCC71D868D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D93F8B42-A188-4907-A14C-A5FB9080AE1E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 09-10-2026'!$A$1:$Z$33</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 23-10-2026'!$A$1:$Z$33</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
